--- a/astro-site/public/dl/guia-panaderia-obrador/plan-financiero-3-anos.xlsx
+++ b/astro-site/public/dl/guia-panaderia-obrador/plan-financiero-3-anos.xlsx
@@ -9,7 +9,9 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="P&amp;L 3 años" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm.Print_Titles" localSheetId="0">'P&amp;L 3 años'!$3:$3</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -462,7 +464,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -481,6 +483,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -611,35 +614,24 @@
       </c>
       <c r="B9">
         <f>SUM(B5:B8)</f>
-        <v/>
+        <v>300000.0</v>
       </c>
       <c r="C9">
         <f>SUM(C5:C8)</f>
-        <v/>
+        <v>402000.0</v>
       </c>
       <c r="D9">
         <f>SUM(D5:D8)</f>
-        <v/>
-      </c>
-      <c r="E9" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr"/>
-      <c r="B10" t="inlineStr"/>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
-    </row>
+        <v>500000.0</v>
+      </c>
+    </row>
+    <row r="10"/>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
           <t>COSTES VARIABLES</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr"/>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
@@ -649,15 +641,15 @@
       </c>
       <c r="B12" s="3">
         <f>B9*0.20</f>
-        <v/>
+        <v>60000.0</v>
       </c>
       <c r="C12" s="3">
         <f>C9*0.19</f>
-        <v/>
+        <v>76380.0</v>
       </c>
       <c r="D12" s="3">
         <f>D9*0.18</f>
-        <v/>
+        <v>90000.0</v>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
@@ -673,15 +665,15 @@
       </c>
       <c r="B13">
         <f>B9*0.015</f>
-        <v/>
+        <v>4500.0</v>
       </c>
       <c r="C13">
         <f>C9*0.015</f>
-        <v/>
+        <v>6030.0</v>
       </c>
       <c r="D13">
         <f>D9*0.015</f>
-        <v/>
+        <v>7500.0</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -697,15 +689,15 @@
       </c>
       <c r="B14">
         <f>B9*0.025</f>
-        <v/>
+        <v>7500.0</v>
       </c>
       <c r="C14">
         <f>C9*0.025</f>
-        <v/>
+        <v>10050.0</v>
       </c>
       <c r="D14">
         <f>D9*0.025</f>
-        <v/>
+        <v>12500.0</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -719,10 +711,6 @@
           <t>COSTES FIJOS</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr"/>
-      <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -865,17 +853,16 @@
       </c>
       <c r="B23">
         <f>SUM(B12:B20)+SUM(B14:B16)</f>
-        <v/>
+        <v>368900.0</v>
       </c>
       <c r="C23">
         <f>SUM(C12:C20)+SUM(C14:C16)</f>
-        <v/>
+        <v>424510.0</v>
       </c>
       <c r="D23">
         <f>SUM(D12:D20)+SUM(D14:D16)</f>
-        <v/>
-      </c>
-      <c r="E23" t="inlineStr"/>
+        <v>475700.0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -885,15 +872,15 @@
       </c>
       <c r="B24">
         <f>B9-B22</f>
-        <v/>
+        <v>300000.0</v>
       </c>
       <c r="C24">
         <f>C9-C22</f>
-        <v/>
+        <v>402000.0</v>
       </c>
       <c r="D24">
         <f>D9-D22</f>
-        <v/>
+        <v>500000.0</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
@@ -909,22 +896,30 @@
       </c>
       <c r="B25">
         <f>B23/B9</f>
-        <v/>
+        <v>1.2296666666666667</v>
       </c>
       <c r="C25">
         <f>C23/C9</f>
-        <v/>
+        <v>1.0559950248756218</v>
       </c>
       <c r="D25">
         <f>D23/D9</f>
-        <v/>
-      </c>
-      <c r="E25" t="inlineStr"/>
+        <v>0.9514</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:E1"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>